--- a/Space Oddity/Physical Arcitecture Systems - Space Oddity.xlsx
+++ b/Space Oddity/Physical Arcitecture Systems - Space Oddity.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1c088fba97fd989/Pictures/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4d14bd4a04985854/Documents/GitHub/AIAA-Systems-Engineering-Workshop/Space Oddity/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{F1A67CE8-83FE-40DF-A4B6-0CE8344C5257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{40DB0116-7804-4C28-AB7A-066080E402DC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{40DB0116-7804-4C28-AB7A-066080E402DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -498,12 +498,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE65C89A-5308-4B94-BCA6-975CA2427D55}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="8.88671875" customWidth="1"/>
+    <col min="1" max="2" width="8.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -511,7 +511,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -519,7 +519,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1.1000000000000001</v>
       </c>
@@ -535,7 +535,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -543,7 +543,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -551,7 +551,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -559,7 +559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1.2</v>
       </c>
@@ -567,7 +567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -575,7 +575,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -583,7 +583,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1.3</v>
       </c>
@@ -591,7 +591,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -599,7 +599,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -607,7 +607,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -615,7 +615,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1.4</v>
       </c>
@@ -623,7 +623,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1.5</v>
       </c>
@@ -631,7 +631,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2</v>
       </c>
@@ -639,7 +639,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2.1</v>
       </c>
@@ -647,7 +647,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2.2000000000000002</v>
       </c>
@@ -655,7 +655,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>9</v>
       </c>

--- a/Space Oddity/Physical Arcitecture Systems - Space Oddity.xlsx
+++ b/Space Oddity/Physical Arcitecture Systems - Space Oddity.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1c088fba97fd989/Pictures/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1c088fba97fd989/Documents/GitHub/AIAA-Systems-Engineering-Workshop/Space Oddity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1A67CE8-83FE-40DF-A4B6-0CE8344C5257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{01E9E6E8-7391-4BB7-A628-4B08291EAEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{40DB0116-7804-4C28-AB7A-066080E402DC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8CCF1B53-05A6-420D-B252-A94D811CA3C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,96 +36,75 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
-  <si>
-    <t>identifier</t>
-  </si>
-  <si>
-    <t>1.1.1</t>
-  </si>
-  <si>
-    <t>1.1.2</t>
-  </si>
-  <si>
-    <t>1.1.3</t>
-  </si>
-  <si>
-    <t>1.2.1</t>
-  </si>
-  <si>
-    <t>1.2.2</t>
-  </si>
-  <si>
-    <t>1.3.1</t>
-  </si>
-  <si>
-    <t>1.3.2</t>
-  </si>
-  <si>
-    <t>1.3.3</t>
-  </si>
-  <si>
-    <t>2.2.1</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>whole system</t>
-  </si>
-  <si>
-    <t>whole plane</t>
-  </si>
-  <si>
-    <t>airframe</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>System-of-System</t>
+  </si>
+  <si>
+    <t>Whole System</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Whole Plane</t>
+  </si>
+  <si>
+    <t>Subsystem</t>
+  </si>
+  <si>
+    <t>Airframe</t>
+  </si>
+  <si>
+    <t>propulsion</t>
+  </si>
+  <si>
+    <t>control</t>
+  </si>
+  <si>
+    <t>computing</t>
+  </si>
+  <si>
+    <t>electrical</t>
+  </si>
+  <si>
+    <t>pilot</t>
+  </si>
+  <si>
+    <t>transmitter</t>
+  </si>
+  <si>
+    <t>ground</t>
+  </si>
+  <si>
+    <t>live telemetry</t>
+  </si>
+  <si>
+    <t>actuating vents</t>
+  </si>
+  <si>
+    <t>tail control surfaces</t>
+  </si>
+  <si>
+    <t>internal ducting</t>
+  </si>
+  <si>
+    <t>turbine</t>
+  </si>
+  <si>
+    <t>tail</t>
+  </si>
+  <si>
+    <t>wings</t>
   </si>
   <si>
     <t>fuselage</t>
   </si>
   <si>
-    <t>wings</t>
-  </si>
-  <si>
-    <t>tail</t>
-  </si>
-  <si>
-    <t>propulsion</t>
-  </si>
-  <si>
-    <t>turbine</t>
-  </si>
-  <si>
-    <t>internal ducting</t>
-  </si>
-  <si>
-    <t>control</t>
-  </si>
-  <si>
-    <t>wing control surfaces</t>
-  </si>
-  <si>
-    <t>tail control surfaces</t>
-  </si>
-  <si>
-    <t>actuating vents</t>
-  </si>
-  <si>
-    <t>computing</t>
-  </si>
-  <si>
-    <t>electrical</t>
-  </si>
-  <si>
-    <t>ground</t>
-  </si>
-  <si>
-    <t>pilot</t>
-  </si>
-  <si>
-    <t>transmitter</t>
-  </si>
-  <si>
-    <t>livemetery</t>
+    <t>element</t>
+  </si>
+  <si>
+    <t>componenet</t>
   </si>
 </sst>
 </file>
@@ -496,171 +475,126 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE65C89A-5308-4B94-BCA6-975CA2427D55}">
-  <dimension ref="A1:B20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44B63EF1-4136-43F7-8CF7-FCAC5B959EC3}">
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1.2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>1.3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>1.4</v>
-      </c>
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>1.5</v>
-      </c>
-      <c r="B16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>2.1</v>
-      </c>
-      <c r="B18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Space Oddity/Physical Arcitecture Systems - Space Oddity.xlsx
+++ b/Space Oddity/Physical Arcitecture Systems - Space Oddity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1c088fba97fd989/Documents/GitHub/AIAA-Systems-Engineering-Workshop/Space Oddity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01E9E6E8-7391-4BB7-A628-4B08291EAEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{01E9E6E8-7391-4BB7-A628-4B08291EAEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{010A21E9-CB6D-4369-84E7-38CBBB306B25}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8CCF1B53-05A6-420D-B252-A94D811CA3C9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>System-of-System</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>componenet</t>
+  </si>
+  <si>
+    <t>wing control surfaces</t>
   </si>
 </sst>
 </file>
@@ -557,6 +560,11 @@
         <v>7</v>
       </c>
     </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
         <v>15</v>
